--- a/vendor_onboarding_hold_queue.xlsx
+++ b/vendor_onboarding_hold_queue.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,21 +32,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -61,9 +53,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,65 +420,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Application ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Vendor Alias</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Current Annual Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Risk Codes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Submitted Date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
@@ -501,7 +478,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>APP-4101</t>
+          <t>APP-5101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -553,22 +530,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>APP-4102</t>
+          <t>APP-5102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NorthBridge Labs; NBL</t>
+          <t>Atlas Hardware; Atlas SG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Medical</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -578,12 +555,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t xml:space="preserve"> 0 </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LOW; MED</t>
+          <t>EXP; LOW</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -593,14 +570,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Singapore</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APP-4103</t>
+          <t>APP-5103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -647,12 +624,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APP-4104</t>
+          <t>APP-5104</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OldTown Medical; OTM</t>
+          <t>Meridian Health; Meridian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -671,11 +648,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SAN; MED</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -685,64 +662,66 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Chicago</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APP-4104</t>
+          <t>APP-5105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OldTown Medical; OTM</t>
+          <t>Nadir Analytics; Nadir</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medical</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ready - resubmitted</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>500</v>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>waived</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SAN; MED</t>
+          <t>PRV; SEC</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Berlin</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APP-4105</t>
+          <t>APP-5106</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Harbor Foods; HF</t>
+          <t>NorthBridge Labs; NBL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -752,7 +731,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Medical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -760,111 +739,244 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>200</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW; MED</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Boston</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APP-4106</t>
+          <t>APP-5107</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GreenVolt Energy; GVE</t>
+          <t>OldTown Medical; OTM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Medical</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>500</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SAN; MED</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APP-4107</t>
+          <t>APP-5107</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nadir Analytics; Nadir</t>
+          <t>OldTown Medical; OTM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Medical</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ready - resubmitted</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>500</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SAN; MED</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>APP-5108</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sentinel Harbor; Sentinel UK</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> waived </t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PRV; SEC</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Berlin</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>APP-5109</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Harbor Foods; HF</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APP-5110</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GreenVolt Energy; GVE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
         </is>
       </c>
     </row>
@@ -879,29 +991,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Office Code</t>
         </is>
@@ -935,16 +1039,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4">
@@ -965,7 +1069,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -974,7 +1078,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6">
@@ -990,6 +1094,66 @@
       </c>
       <c r="C6" t="n">
         <v>230</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1003,22 +1167,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Search Volume</t>
         </is>
@@ -1040,87 +1198,177 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Root matching must use complete words.</t>
+          <t>Root matching uses vendor-scoped phrase filtering plus complete-word root matching.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>apex cn baseline kyc</t>
+          <t>apex components sourcing request</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>northbridge medical onboarding</t>
+          <t>atlas hardware sourcing qa</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cobalt za mining review</t>
+          <t>atlas hardware export filing</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>oldtown medical sanctions</t>
+          <t>cobalt mining permit review</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>oldtown sanctions resubmitted</t>
+          <t>meridian health medical intake</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nadir security analytics</t>
+          <t>meridian health sanctions list</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>harbor food low risk</t>
+          <t>nadir analytics security analytics</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>nadir analytics privacy audit</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>northbridge labs medical onboarding</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>northbridge labs sanctions review</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>oldtown medical sanctions screening</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>oldtown medical sanctions resubmitted</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>oldtown medical medical device intake</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sentinel harbor privacy assessment</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sentinel harbor security monitor</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>harbor foods low risk</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>medicalized vendor text</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B19" t="n">
         <v>999</v>
       </c>
     </row>
@@ -1135,20 +1383,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Applies To Category</t>
         </is>
@@ -1169,24 +1413,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>sourcing</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Medical</t>
+          <t>Hardware</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mining</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -1205,22 +1449,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Mining</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>privacy</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
@@ -1237,38 +1505,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Vendor Canonical</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Game 1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Game 2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Game 3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Game 4</t>
         </is>
@@ -1296,20 +1557,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NorthBridge Labs</t>
+          <t>Atlas Hardware</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
         <v>8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1334,20 +1595,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OldTown Medical</t>
+          <t>Meridian Health</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1366,6 +1627,63 @@
         <v>11</v>
       </c>
       <c r="E6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NorthBridge Labs</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OldTown Medical</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sentinel Harbor</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1382,36 +1700,29 @@
   </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Rule Type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Match Key</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Review Group</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Requires Manual Review</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Hold Reason</t>
         </is>
@@ -1673,30 +1984,24 @@
   </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Vendor Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Vendor ID</t>
         </is>
@@ -1779,64 +2084,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Application ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Canonical Vendor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Office Code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Matched Root</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Matched Search Volume</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Win Count</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Spend Status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Trigger Type</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Trigger Key</t>
         </is>
@@ -1850,19 +2142,10 @@
     <row r="2">
       <c r="K2" t="inlineStr">
         <is>
-          <t>Only A2:I11 is scored output.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
+          <t>Only A2:I13 is scored output.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
